--- a/viewer/downloads/CC3_Alignment.xlsx
+++ b/viewer/downloads/CC3_Alignment.xlsx
@@ -670,12 +670,12 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2022), 8.1.1.5 (MN-2022), 8.1.1.6 (MN-2022), 8.SP.2 (CCSS-M), 8.SP.A.1 (CCSS-M), 8.SP.A.2 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2022), 8.1.1.5 (MN-2022), 8.1.1.6 (MN-2022), 8.4.1.1 (MN-2007), 8.4.1.2 (MN-2007), 8.SP.2 (CCSS-M), 8.SP.A.1 (CCSS-M), 8.SP.A.2 (CCSS-M)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>7.EE.A.1 (CCSS-M), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.EE.A.1 (CCSS-M), 8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.3.6.2 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.2 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>7.EE.B.4.B (CCSS-M), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.EE.B.4.B (CCSS-M), 8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>7.EE.B.4.B (CCSS-M), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.EE.B.4.B (CCSS-M), 8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.2 (MN-2022), 8.3.7.6 (MN-2022), 8.F.1 (CCSS-M), 8.F.A.1 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.2 (MN-2022), 8.3.7.6 (MN-2022), 8.F.1 (CCSS-M), 8.F.A.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>8.2.4.1 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.7.1 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.2 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.2 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.1 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.1 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>8.2.4.1 (MN-2022), 8.3.7.3 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.B.5 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.7.3 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.B.5 (CCSS-M)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.4 (MN-2022), 8.3.7.6 (MN-2022), 8.F.4 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.4 (MN-2022), 8.3.7.6 (MN-2022), 8.F.4 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.1 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.1 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.1 (MN-2022), 8.3.6.3 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.1 (MN-2022), 8.3.6.3 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.6 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.6 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.5 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.5 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.6 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.5 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.6 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.5 (CCSS-M)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.3 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.B.8 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.B.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.3 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.B.7 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.B.7 (CCSS-M)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.9 (MN-2022), 8.EE.8a (CCSS-M), 8.EE.A.8 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.9 (MN-2022), 8.EE.8a (CCSS-M), 8.EE.A.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>8.2.4.3 (MN-2022), 8.3.6.9 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.8c (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.3 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.6.9 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.8c (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), 8.G.3 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), 8.G.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.2 (MN-2022), See eBook (CCSS-M)</t>
+          <t>8.1.1.2 (MN-2022), 8.4.1.1 (MN-2007), 8.4.1.2 (MN-2007), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2022), 8.1.1.2 (MN-2022), 8.1.1.4 (MN-2022), 8.1.1.6 (MN-2022), 8.SP.1 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2022), 8.1.1.2 (MN-2022), 8.1.1.4 (MN-2022), 8.1.1.6 (MN-2022), 8.4.1.1 (MN-2007), 8.4.1.2 (MN-2007), 8.SP.1 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.3.5.8 (MN-2022), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.6 (MN-2022), 8.EE.6 (CCSS-M), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.5.8 (MN-2022), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.6 (MN-2022), 8.EE.6 (CCSS-M), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.1 (MN-2022), 8.EE.5 (CCSS-M), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.1 (MN-2022), 8.EE.5 (CCSS-M), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2584,12 +2584,12 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.3 (MN-2022), 8.SP.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.3 (MN-2022), 8.4.1.1 (MN-2007), 8.4.1.2 (MN-2007), 8.SP.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2022), 8.1.1.3 (MN-2022), 8.1.1.4 (MN-2022), 8.1.1.5 (MN-2022), 8.1.1.6 (MN-2022), 8.SP.2 (CCSS-M), 8.SP.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2022), 8.1.1.3 (MN-2022), 8.1.1.4 (MN-2022), 8.1.1.5 (MN-2022), 8.1.1.6 (MN-2022), 8.4.1.1 (MN-2007), 8.4.1.2 (MN-2007), 8.SP.2 (CCSS-M), 8.SP.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2022), 8.SP.4 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2022), 8.4.1.1 (MN-2007), 8.4.1.2 (MN-2007), 8.SP.4 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>8.2.4.1 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.7.3 (MN-2022), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.7.3 (MN-2022), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>8.2.4.1 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.7.3 (MN-2022), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.7.3 (MN-2022), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>8.3.5.3 (MN-2022), 8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.EE.1 (CCSS-M), 8.EE.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.5.3 (MN-2022), 8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.EE.1 (CCSS-M), 8.EE.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>8.3.5.3 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.5.3 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2908,12 +2908,12 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.EE.4 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.EE.4 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2943,12 +2943,12 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.3 (MN-2022), 8.3.7.6 (MN-2022), 8.F.1 (CCSS-M), 8.F.3 (CCSS-M), 8.F.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.3 (MN-2022), 8.3.7.6 (MN-2022), 8.F.1 (CCSS-M), 8.F.3 (CCSS-M), 8.F.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2991,12 +2991,12 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3061,12 +3061,12 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>8.2.3.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.6.4 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.1 (MN-2022), 8.2.3.2 (MN-2007), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.5.2 (MN-2022), 8.3.6.4 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3096,12 +3096,12 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.6.4 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.6.4 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3361,12 +3361,12 @@
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.7 (MN-2022), 8.EE.2 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.7 (MN-2022), 8.EE.2 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.7 (MN-2022), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.7 (MN-2022), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.8 (MN-2022), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.8 (MN-2022), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3530,12 +3530,12 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.9 (MN-2022), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.9 (MN-2022), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3619,12 +3619,12 @@
       <c r="E102" s="7" t="inlineStr"/>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.9 (MN-2022)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.9 (MN-2022)</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022, mn_correlation</t>
         </is>
       </c>
     </row>

--- a/viewer/downloads/CC3_Alignment.xlsx
+++ b/viewer/downloads/CC3_Alignment.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>8.EE.B.5 (CCSS-M), 8.F.A.3 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.B.5 (CCSS-M), 8.F.A.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>8.EE.5 (CCSS-M), 8.F.A.2 (CCSS-M)</t>
+          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.EE.5 (CCSS-M), 8.F.A.2 (CCSS-M)</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -733,12 +733,12 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>7.RP.A.2.A (CCSS-M), 8.EE.7a (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.RP.A.2.A (CCSS-M), 8.EE.7a (CCSS-M)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>7.EE.A.1 (CCSS-M), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.A.1 (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>7.EE.A.1 (CCSS-M), 8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.A.1 (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>7.EE.A.1 (CCSS-M), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.A.1 (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.2 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.2 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>7.EE.B.4.B (CCSS-M), 8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.B.4.B (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>7.EE.B.4.B (CCSS-M), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.B.4.B (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>7.EE.B.4.B (CCSS-M), 8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.B.4.B (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.2 (MN-2022), 8.3.7.6 (MN-2022), 8.F.1 (CCSS-M), 8.F.A.1 (CCSS-M)</t>
+          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.3.7.2 (MN-2022), 8.3.7.6 (MN-2022), 8.F.1 (CCSS-M), 8.F.A.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.7.1 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.4.1 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.2 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.7.2 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.1 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.7.1 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.7.3 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.B.5 (CCSS-M)</t>
+          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.4.1 (MN-2022), 8.3.7.3 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.B.5 (CCSS-M)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.4 (MN-2022), 8.3.7.6 (MN-2022), 8.F.4 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.7.4 (MN-2022), 8.3.7.6 (MN-2022), 8.F.4 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.1 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.7.1 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.1 (MN-2022), 8.3.6.3 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.1 (MN-2022), 8.3.6.3 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.6 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.6 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.5 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.5 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>8.EE.6 (CCSS-M), 8.EE.B.6 (CCSS-M), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.6 (CCSS-M), 8.EE.B.6 (CCSS-M), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.6 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.5 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.6 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.5 (CCSS-M)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.B.8 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.B.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.B.7 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.B.7 (CCSS-M)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.9 (MN-2022), 8.EE.8a (CCSS-M), 8.EE.A.8 (CCSS-M)</t>
+          <t>8.1.2.1 (MN-2007), 8.3.6.9 (MN-2022), 8.EE.8a (CCSS-M), 8.EE.A.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>8.EE.8c (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
+          <t>8.2.3.2 (MN-2007), 8.EE.8c (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>8.EE.8b (CCSS-M), 8.EE.8c (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.EE.8b (CCSS-M), 8.EE.8c (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.3 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.6.9 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.8c (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.3 (MN-2022), 8.3.6.9 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.8c (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
+          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
+          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
+          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), 8.G.3 (CCSS-M)</t>
+          <t>8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), 8.G.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, mn_correlation</t>
+          <t>ccss_lesson_guide, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M)</t>
+          <t>8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, mn_correlation</t>
+          <t>ccss_lesson_guide, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
+          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.5.8 (MN-2022), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.6 (MN-2022), 8.EE.6 (CCSS-M), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.3.5.8 (MN-2022), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.6 (MN-2022), 8.EE.6 (CCSS-M), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.1 (MN-2022), 8.EE.5 (CCSS-M), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.7.1 (MN-2022), 8.EE.5 (CCSS-M), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.7.3 (MN-2022), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.4.1 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.7.3 (MN-2022), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.7.3 (MN-2022), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.4.1 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.7.3 (MN-2022), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.5.3 (MN-2022), 8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.EE.1 (CCSS-M), 8.EE.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.5.3 (MN-2022), 8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.EE.1 (CCSS-M), 8.EE.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.5.3 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.5.3 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2908,12 +2908,12 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.EE.4 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.EE.4 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2943,12 +2943,12 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.7.3 (MN-2022), 8.3.7.6 (MN-2022), 8.F.1 (CCSS-M), 8.F.3 (CCSS-M), 8.F.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.7.3 (MN-2022), 8.3.7.6 (MN-2022), 8.F.1 (CCSS-M), 8.F.3 (CCSS-M), 8.F.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.3.3.1 (MN-2007), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.3.3.1 (MN-2007), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.1 (MN-2022), 8.2.3.2 (MN-2007), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.5.2 (MN-2022), 8.3.6.4 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.3.3.1 (MN-2007), 8.3.5.2 (MN-2022), 8.3.6.4 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.6.4 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.6.4 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3361,12 +3361,12 @@
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.7 (MN-2022), 8.EE.2 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.6.7 (MN-2022), 8.EE.2 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.7 (MN-2022), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.6.7 (MN-2022), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.8 (MN-2022), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.6.8 (MN-2022), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3530,12 +3530,12 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.9 (MN-2022), See eBook (CCSS-M)</t>
+          <t>8.3.6.9 (MN-2022), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, mn_correlation</t>
+          <t>ccss_lesson_guide, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3619,12 +3619,12 @@
       <c r="E102" s="7" t="inlineStr"/>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.9 (MN-2022)</t>
+          <t>8.3.6.9 (MN-2022)</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>

--- a/viewer/downloads/CC3_Alignment.xlsx
+++ b/viewer/downloads/CC3_Alignment.xlsx
@@ -701,7 +701,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.EE.5 (CCSS-M), 8.F.A.2 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.5 (CCSS-M), 8.F.A.2 (CCSS-M)</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.RP.A.2.A (CCSS-M), 8.EE.7a (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.RP.A.2.A (CCSS-M), 8.EE.7a (CCSS-M)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.A.1 (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.A.1 (CCSS-M), 8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.2 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.2 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.B.4.B (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.B.4.B (CCSS-M), 8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.B.4.B (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.B.4.B (CCSS-M), 8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.1 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.4.1 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.4.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.7.1 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.4.1 (MN-2022), 8.3.7.3 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.B.5 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.4.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.7.3 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.B.5 (CCSS-M)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7a (CCSS-M), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.7.1 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.7.1 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.1 (MN-2022), 8.3.6.3 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.1 (MN-2022), 8.3.6.3 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.B.8 (CCSS-M)</t>
+          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.B.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.B.7 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.6.3 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.B.7 (CCSS-M)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>8.1.2.1 (MN-2007), 8.3.6.9 (MN-2022), 8.EE.8a (CCSS-M), 8.EE.A.8 (CCSS-M)</t>
+          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.2 (MN-2007), 8.3.6.9 (MN-2022), 8.EE.8a (CCSS-M), 8.EE.A.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.EE.8b (CCSS-M), 8.EE.8c (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
+          <t>8.2.3.2 (MN-2007), 8.EE.8b (CCSS-M), 8.EE.8c (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.3 (MN-2022), 8.3.6.9 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.8c (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
+          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.3 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.6.9 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.8c (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
+          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
+          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
+          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>8.G.3 (CCSS-M)</t>
+          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), 8.G.3 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), 8.G.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
+          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>8.G.2 (CCSS-M), 8.G.4 (CCSS-M)</t>
+          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.2 (CCSS-M), 8.G.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -2241,12 +2241,12 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>8.G.4 (CCSS-M)</t>
+          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>8.G.4 (CCSS-M)</t>
+          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_ccss, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2386,12 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>8.SP.1 (CCSS-M), 8.SP.2 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.4.1.1 (MN-2007), 8.4.1.2 (MN-2007), 8.SP.1 (CCSS-M), 8.SP.2 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.3.5.8 (MN-2022), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.6 (MN-2022), 8.EE.6 (CCSS-M), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.5.8 (MN-2022), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.6 (MN-2022), 8.EE.6 (CCSS-M), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.1 (MN-2022), 8.EE.5 (CCSS-M), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.7.1 (MN-2022), 8.EE.5 (CCSS-M), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>8.2.4.1 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.7.3 (MN-2022), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.7.3 (MN-2022), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>8.2.4.1 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.7.3 (MN-2022), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.1.2.1 (MN-2007), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.2.3.2 (MN-2007), 8.2.4.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.7.3 (MN-2022), 8.F.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>8.3.5.3 (MN-2022), 8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.EE.1 (CCSS-M), 8.EE.3 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.2.1 (MN-2007), 8.3.5.3 (MN-2022), 8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.EE.1 (CCSS-M), 8.EE.3 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>8.3.5.3 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.2.1 (MN-2007), 8.3.5.3 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2908,12 +2908,12 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.EE.4 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.2.1 (MN-2007), 8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.EE.4 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2943,12 +2943,12 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>8.3.7.3 (MN-2022), 8.3.7.6 (MN-2022), 8.F.1 (CCSS-M), 8.F.3 (CCSS-M), 8.F.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.7.3 (MN-2022), 8.3.7.6 (MN-2022), 8.F.1 (CCSS-M), 8.F.3 (CCSS-M), 8.F.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.3.3.1 (MN-2007), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.3.3.1 (MN-2007), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>8.2.3.1 (MN-2022), 8.3.3.1 (MN-2007), 8.3.5.2 (MN-2022), 8.3.6.4 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.2.3.1 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.5.2 (MN-2022), 8.3.6.4 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.6.4 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.6.4 (MN-2022), 8.G.5 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>8.G.7 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.G.7 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3158,12 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>8.G.6 (CCSS-M), 8.G.7 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.G.6 (CCSS-M), 8.G.7 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>8.EE.2 (CCSS-M), 8.NS.2 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.EE.2 (CCSS-M), 8.NS.2 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>8.EE.2 (CCSS-M), 8.NS.1 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.EE.2 (CCSS-M), 8.NS.1 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>8.G.7 (CCSS-M), 8.G.8 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.G.7 (CCSS-M), 8.G.8 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>8.G.7 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.G.7 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3361,12 +3361,12 @@
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.7 (MN-2022), 8.EE.2 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.3.6.7 (MN-2022), 8.EE.2 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.7 (MN-2022), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.6.7 (MN-2022), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.8 (MN-2022), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.3.3.1 (MN-2007), 8.3.6.8 (MN-2022), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.3.1 (MN-2007), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3495,12 +3495,12 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.3.1 (MN-2007), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3530,12 +3530,12 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.9 (MN-2022), See eBook (CCSS-M)</t>
+          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.3.6.9 (MN-2022), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3619,12 +3619,12 @@
       <c r="E102" s="7" t="inlineStr"/>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>8.3.6.9 (MN-2022)</t>
+          <t>8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.3.6.9 (MN-2022)</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022, mn_correlation</t>
         </is>
       </c>
     </row>

--- a/viewer/downloads/CC3_Alignment.xlsx
+++ b/viewer/downloads/CC3_Alignment.xlsx
@@ -76,12 +76,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -594,20 +594,24 @@
           <t>Pattern Recognition</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.8, 8.3.6.3, 8.3.6.5, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.7, 8.3.7.8, 8.3.7.9</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>MP4, MP8</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>MP4 (CCSS-M), MP8 (CCSS-M)</t>
+          <t>8.3.5.8 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.6 (MN-2022), 8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.3.7.9 (MN-2022), MP4 (CCSS-M), MP8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide</t>
+          <t>bridged_via_content, ccss_lesson_guide</t>
         </is>
       </c>
     </row>
@@ -626,15 +630,19 @@
 Linear Graphs</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.9</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>8.EE.B.5, 8.F.A.3</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.B.5 (CCSS-M), 8.F.A.3 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.6.1 (MN-2022), 8.3.6.2 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.4 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.6 (MN-2022), 8.3.7.9 (MN-2022), 8.EE.B.5 (CCSS-M), 8.F.A.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -658,12 +666,12 @@
 Independent and Dependent measurements</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>8.1.1.1, 8.1.1.5, 8.1.1.6</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>8.SP.2, 8.SP.A.1, 8.SP.A.2</t>
         </is>
@@ -693,15 +701,19 @@
           <t>Proportinal Relationships</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.9</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>8.EE.5, 8.F.A.2</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.5 (CCSS-M), 8.F.A.2 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.6.1 (MN-2022), 8.3.6.2 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.4 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.6 (MN-2022), 8.3.7.9 (MN-2022), 8.EE.5 (CCSS-M), 8.F.A.2 (CCSS-M)</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -725,15 +737,19 @@
 Solving Proportions</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4, 7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>7.RP.A.2.A, 8.EE.7a</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.RP.A.2.A (CCSS-M), 8.EE.7a (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.2.4.1 (MN-2022), 7.2.4.2 (MN-2022), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.5.7 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.A.2.A (CCSS-M), 8.EE.7a (CCSS-M)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -770,15 +786,19 @@
 Simplyfiing Expressions</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>7.EE.A.1, 8.EE.7a, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.A.1 (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.EE.A.1 (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -802,12 +822,12 @@
 Simplyfiing Expressions</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>8.3.6.1</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>7.EE.A.1, 8.EE.7a, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
@@ -837,15 +857,19 @@
           <t>Simplifying Algebraic Expressions</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>7.EE.A.1, 8.EE.7a, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.A.1 (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.EE.A.1 (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -869,12 +893,12 @@
 Simplifying Aglebraic Expressions</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>8.3.6.2</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>7.EE.A.1.A, 7.EE.A.1.B, 8.EE.7a, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
@@ -905,12 +929,12 @@
 Simplifying Expressions</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>8.3.6.1</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>7.EE.B.4.B, 8.EE.7a, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
@@ -941,15 +965,19 @@
 Simplifying Aglebraic Expressions</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>7.EE.B.4.B, 8.EE.7a, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.B.4.B (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.EE.B.4.B (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.7a (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -973,12 +1001,12 @@
 Simplifying Aglebraic Expressions</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>8.3.6.1</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>7.EE.B.4.B, 8.EE.7a, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
@@ -1008,12 +1036,12 @@
           <t>Simplifying and Solving Aglebraic Expressions</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>8.3.6.3</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>8.EE.7a, 8.EE.7b, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
@@ -1043,12 +1071,12 @@
           <t>Simplifying and Solving Aglebraic Expressions</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>8.3.6.3</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>8.EE.7a, 8.EE.7b, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
@@ -1091,12 +1119,12 @@
           <t>Connecting Rules and Patterns</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>8.3.7.2, 8.3.7.6</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>8.F.1, 8.F.A.1</t>
         </is>
@@ -1126,12 +1154,12 @@
           <t>Writing Algebraic Equations</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>8.2.4.1, 8.3.7.1, 8.3.7.3, 8.3.7.4</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>8.F.1, 8.F.2, 8.F.3, 8.F.4, 8.F.A.1, 8.F.A.2, 8.F.A.3, 8.F.B.4</t>
         </is>
@@ -1161,12 +1189,12 @@
           <t>Graphing Equations</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>8.3.7.2</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>8.F.1, 8.F.2, 8.F.3, 8.F.4, 8.F.A.1, 8.F.B.4</t>
         </is>
@@ -1196,15 +1224,19 @@
           <t>Graphing Data</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.8, 8.3.6.3, 8.3.6.5, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.7, 8.3.7.8</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>8.F.1, 8.F.2, 8.F.3, 8.F.4, 8.F.A.1, 8.F.B.4</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.5.8 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.6 (MN-2022), 8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.F.1 (CCSS-M), 8.F.2 (CCSS-M), 8.F.3 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.1 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1227,12 +1259,12 @@
           <t>Graphing Data</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>8.3.7.1</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>8.F.1, 8.F.2, 8.F.3, 8.F.4, 8.F.A.1, 8.F.B.4</t>
         </is>
@@ -1262,12 +1294,12 @@
           <t>Graphing Equations</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>8.2.4.1, 8.3.7.3</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>8.F.1, 8.F.2, 8.F.3, 8.F.4, 8.F.B.5</t>
         </is>
@@ -1297,12 +1329,12 @@
           <t>Interpreting Graphs</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>8.3.7.4, 8.3.7.6</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>8.F.4, 8.F.B.4</t>
         </is>
@@ -1332,12 +1364,12 @@
           <t>Solving Equations</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>8.3.6.3</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>8.EE.7a, 8.EE.7b, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
@@ -1367,12 +1399,12 @@
           <t>Solving Equations</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>8.3.6.3</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>8.EE.7a, 8.EE.7b, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
@@ -1402,15 +1434,19 @@
           <t>Solving Equations</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.9</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>8.EE.7b, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.6.1 (MN-2022), 8.3.6.2 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.4 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.9 (MN-2022), 8.EE.7b (CCSS-M), 8.EE.C.7.A (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -1433,12 +1469,12 @@
           <t>Solving Equations</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>8.3.7.1</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>8.EE.7b, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
@@ -1468,12 +1504,12 @@
           <t>Solving Equations</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>8.3.6.1, 8.3.6.3</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>8.EE.7b, 8.EE.C.7.A, 8.EE.C.7.B</t>
         </is>
@@ -1516,12 +1552,12 @@
           <t>Pattern Recognition</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>8.3.7.1, 8.3.7.2, 8.3.7.4, 8.3.7.6</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>8.F.2, 8.F.4, 8.F.A.2, 8.F.B.4</t>
         </is>
@@ -1551,15 +1587,19 @@
           <t>Writing Linear Equations</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.8, 8.3.6.3, 8.3.6.5, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.7, 8.3.7.8</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>8.F.2, 8.F.4, 8.F.A.2, 8.F.B.4</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.5.8 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.6 (MN-2022), 8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -1582,12 +1622,12 @@
           <t>Graphing Linear Equations</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>8.3.6.5, 8.3.6.6, 8.3.7.2, 8.3.7.5</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>8.F.2, 8.F.4, 8.F.A.2, 8.F.B.4</t>
         </is>
@@ -1617,15 +1657,19 @@
           <t>Writing Linear Equations</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr"/>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.9</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>8.EE.6, 8.EE.B.6, 8.F.2, 8.F.4, 8.F.A.2, 8.F.B.4</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.6 (CCSS-M), 8.EE.B.6 (CCSS-M), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.6.1 (MN-2022), 8.3.6.2 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.4 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.6 (MN-2022), 8.3.7.9 (MN-2022), 8.EE.6 (CCSS-M), 8.EE.B.6 (CCSS-M), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.2 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -1648,12 +1692,12 @@
           <t>Making Connections between Representations</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>8.3.6.5, 8.3.6.6</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>8.F.2, 8.F.4, 8.F.A.2, 8.F.B.4</t>
         </is>
@@ -1683,15 +1727,19 @@
           <t>Graphing Linear Equations</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.8, 8.3.6.3, 8.3.6.5, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.7, 8.3.7.8</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>8.F.2, 8.F.4, 8.F.A.3, 8.F.B.4</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.2.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.5.8 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.5 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.6 (MN-2022), 8.3.7.7 (MN-2022), 8.3.7.8 (MN-2022), 8.F.2 (CCSS-M), 8.F.4 (CCSS-M), 8.F.A.3 (CCSS-M), 8.F.B.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -1714,12 +1762,12 @@
           <t>Making Connections between Representations</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>8.3.7.1, 8.3.7.2, 8.3.7.4, 8.3.7.6</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>8.F.2, 8.F.4, 8.F.A.3, 8.F.B.5</t>
         </is>
@@ -1762,12 +1810,12 @@
           <t>Isolating Variables in Equations</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>8.3.6.3</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>8.EE.8b, 8.EE.B.8</t>
         </is>
@@ -1797,12 +1845,12 @@
           <t>Solving equations with Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>8.3.6.3</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>8.EE.7b, 8.EE.B.7</t>
         </is>
@@ -1832,12 +1880,12 @@
           <t>Introduce Systems of Equations</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>8.3.6.9</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>8.EE.8a, 8.EE.A.8</t>
         </is>
@@ -1867,15 +1915,19 @@
           <t>Writing Rules from Word Problems</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr"/>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.9</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>8.EE.8c, 8.EE.C.8</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>8.2.3.2 (MN-2007), 8.EE.8c (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
+          <t>8.2.3.2 (MN-2007), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.6.1 (MN-2022), 8.3.6.2 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.4 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.9 (MN-2022), 8.EE.8c (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -1898,15 +1950,19 @@
           <t>Solving Systems</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr"/>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.9</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>8.EE.8b, 8.EE.8c, 8.EE.B.8, 8.EE.C.8</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>8.2.3.2 (MN-2007), 8.EE.8b (CCSS-M), 8.EE.8c (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
+          <t>8.2.3.2 (MN-2007), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.6.1 (MN-2022), 8.3.6.2 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.4 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.9 (MN-2022), 8.EE.8b (CCSS-M), 8.EE.8c (CCSS-M), 8.EE.B.8 (CCSS-M), 8.EE.C.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -1929,12 +1985,12 @@
           <t>Sovling Systems</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>8.2.4.3, 8.3.6.9</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>8.EE.8b, 8.EE.8c, 8.EE.B.8, 8.EE.C.8</t>
         </is>
@@ -1977,15 +2033,19 @@
           <t>Rigid Transformations</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr"/>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>8.G.1a, 8.G.1b, 8.G.1c, 8.G.A.1, 8.G.B.1, 8.G.C.1</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -2008,15 +2068,19 @@
           <t>Rigid Transformations</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr"/>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>8.G.1a, 8.G.1b, 8.G.1c, 8.G.2, 8.G.3, 8.G.4, 8.G.A.1, 8.G.B.1, 8.G.C.1</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -2039,15 +2103,19 @@
           <t>Rigid Transformations</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr"/>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>8.G.1a, 8.G.1b, 8.G.1c, 8.G.2, 8.G.3, 8.G.4, 8.G.A.1, 8.G.B.1, 8.G.C.1</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.3 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
@@ -2070,15 +2138,19 @@
           <t>Rigid Transformations</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr"/>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>8.G.3</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.3 (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
@@ -2101,12 +2173,12 @@
           <t>Dilations</t>
         </is>
       </c>
-      <c r="D54" s="9" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>8.3.7.7, 8.3.7.8, 8.3.7.9</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>8.G.3</t>
         </is>
@@ -2136,12 +2208,12 @@
           <t>Dilations and Similarity</t>
         </is>
       </c>
-      <c r="D55" s="9" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>8.3.7.7, 8.3.7.8, 8.3.7.9</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>8.G.3, 8.G.4</t>
         </is>
@@ -2171,15 +2243,19 @@
           <t>Similarity, Congruence, and Scale Factor</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr"/>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>8.G.1a, 8.G.1b, 8.G.1c, 8.G.2, 8.G.4, 8.G.A.1, 8.G.B.1, 8.G.C.1</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.1a (CCSS-M), 8.G.1b (CCSS-M), 8.G.1c (CCSS-M), 8.G.2 (CCSS-M), 8.G.4 (CCSS-M), 8.G.A.1 (CCSS-M), 8.G.B.1 (CCSS-M), 8.G.C.1 (CCSS-M)</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -2202,15 +2278,19 @@
           <t>Similar Figures &amp; Transformations</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr"/>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>8.G.2, 8.G.4</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.2 (CCSS-M), 8.G.4 (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.2 (CCSS-M), 8.G.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -2233,15 +2313,19 @@
           <t>Similar Figures</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr"/>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>8.G.4</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.4 (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -2264,15 +2348,19 @@
           <t>Similar Figures</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr"/>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>8.G.4</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.4 (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.2.1 (MN-2007), 8.3.2.2 (MN-2007), 8.G.4 (CCSS-M)</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -2308,12 +2396,12 @@
           <t>Circle Graphs</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>8.1.1.2</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>See eBook</t>
         </is>
@@ -2343,12 +2431,12 @@
           <t>Scatterplots &amp; Data</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>8.1.1.1, 8.1.1.2, 8.1.1.4, 8.1.1.6</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>8.SP.1, See eBook</t>
         </is>
@@ -2378,15 +2466,19 @@
           <t>Scatterplots &amp; Association</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr"/>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>8.1.1.1, 8.1.1.2, 8.1.1.3, 8.1.1.4, 8.1.1.5, 8.1.1.6</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>8.SP.1, 8.SP.2, See eBook</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>8.4.1.1 (MN-2007), 8.4.1.2 (MN-2007), 8.SP.1 (CCSS-M), 8.SP.2 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2022), 8.1.1.2 (MN-2022), 8.1.1.3 (MN-2022), 8.1.1.4 (MN-2022), 8.1.1.5 (MN-2022), 8.1.1.6 (MN-2022), 8.4.1.1 (MN-2007), 8.4.1.2 (MN-2007), 8.SP.1 (CCSS-M), 8.SP.2 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -2409,12 +2501,12 @@
           <t>Linear graphs and equations</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>8.2.4.1, 8.2.4.2, 8.3.5.8, 8.3.6.5, 8.3.6.6, 8.3.7.1, 8.3.7.3, 8.3.7.6</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>8.EE.6, 8.F.3, See eBook</t>
         </is>
@@ -2444,15 +2536,19 @@
           <t>Slope</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr"/>
-      <c r="E65" s="8" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.9</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>8.EE.6, See eBook</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.6.1 (MN-2022), 8.3.6.2 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.4 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.6 (MN-2022), 8.3.7.9 (MN-2022), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -2475,15 +2571,19 @@
           <t>Slope</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr"/>
-      <c r="E66" s="8" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.9</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>8.EE.6, See eBook</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.6.1 (MN-2022), 8.3.6.2 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.4 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.6 (MN-2022), 8.3.7.9 (MN-2022), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -2506,15 +2606,19 @@
           <t>Slope</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr"/>
-      <c r="E67" s="8" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.1, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.6, 8.3.7.9</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
         <is>
           <t>8.EE.6, See eBook</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.2.1 (MN-2007), 8.2.3.1 (MN-2007), 8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.6.1 (MN-2022), 8.3.6.2 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.4 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.1 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.6 (MN-2022), 8.3.7.9 (MN-2022), 8.EE.6 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -2537,12 +2641,12 @@
           <t>Proportional Equations</t>
         </is>
       </c>
-      <c r="D68" s="9" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>8.3.7.1</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E68" s="9" t="inlineStr">
         <is>
           <t>8.EE.5, 8.EE.6, See eBook</t>
         </is>
@@ -2572,12 +2676,12 @@
           <t>Line of Best Fit Equation</t>
         </is>
       </c>
-      <c r="D69" s="9" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>8.1.1.3</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr">
         <is>
           <t>8.SP.3, See eBook</t>
         </is>
@@ -2607,12 +2711,12 @@
           <t>Line of Best Fit Equation &amp; Association</t>
         </is>
       </c>
-      <c r="D70" s="9" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>8.1.1.1, 8.1.1.3, 8.1.1.4, 8.1.1.5, 8.1.1.6</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
+      <c r="E70" s="9" t="inlineStr">
         <is>
           <t>8.SP.2, 8.SP.3, See eBook</t>
         </is>
@@ -2642,12 +2746,12 @@
           <t>Two-Way Tables &amp; Association</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>8.1.1.1</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
+      <c r="E71" s="9" t="inlineStr">
         <is>
           <t>8.SP.4, See eBook</t>
         </is>
@@ -2690,12 +2794,12 @@
           <t>Linear &amp; Nonlinear Tables &amp; Graphs</t>
         </is>
       </c>
-      <c r="D73" s="9" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>8.2.4.1, 8.3.5.6, 8.3.5.7, 8.3.7.3</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E73" s="9" t="inlineStr">
         <is>
           <t>8.F.3, See eBook</t>
         </is>
@@ -2725,12 +2829,12 @@
           <t>Compound Interest</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>8.3.5.6, 8.3.5.7</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="E74" s="9" t="inlineStr">
         <is>
           <t>8.EE.1, See eBook</t>
         </is>
@@ -2760,12 +2864,12 @@
           <t>Simple Interest (Linear) &amp; Compound Interest (Exponential Growth)</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>8.2.4.1, 8.3.5.6, 8.3.5.7, 8.3.7.3</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="E75" s="9" t="inlineStr">
         <is>
           <t>8.F.3, See eBook</t>
         </is>
@@ -2795,12 +2899,12 @@
           <t>Positive Exponents &amp; Scientific Notation</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>8.3.5.3, 8.3.5.4, 8.3.5.5</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E76" s="9" t="inlineStr">
         <is>
           <t>8.EE.1, 8.EE.3, See eBook</t>
         </is>
@@ -2830,20 +2934,24 @@
           <t>Simplifying Exponents (Properties of Exponents)</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr"/>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.5.4, 8.3.5.5, 8.3.6.4, 8.3.7.3</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
         <is>
           <t>8.EE.1, See eBook</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.5.4 (MN-2022), 8.3.5.5 (MN-2022), 8.3.6.4 (MN-2022), 8.3.7.3 (MN-2022), 8.EE.1 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2969,12 @@
           <t>Negative Exponents &amp; Scientific Notation</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>8.3.5.3</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E78" s="9" t="inlineStr">
         <is>
           <t>8.EE.1, See eBook</t>
         </is>
@@ -2896,12 +3004,12 @@
           <t>Operations with Scientific Notation</t>
         </is>
       </c>
-      <c r="D79" s="9" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>8.3.5.4, 8.3.5.5</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="E79" s="9" t="inlineStr">
         <is>
           <t>8.EE.4, See eBook</t>
         </is>
@@ -2931,12 +3039,12 @@
           <t>Intro to Functions</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>8.3.7.3, 8.3.7.6</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
+      <c r="E80" s="9" t="inlineStr">
         <is>
           <t>8.F.1, 8.F.3, 8.F.5, See eBook</t>
         </is>
@@ -2979,12 +3087,12 @@
           <t>Parallel Lines Cut by a Transversal</t>
         </is>
       </c>
-      <c r="D82" s="9" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>8.2.3.1, 8.2.3.2, 8.2.3.3</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="E82" s="9" t="inlineStr">
         <is>
           <t>8.G.5, See eBook</t>
         </is>
@@ -3014,12 +3122,12 @@
           <t>Triangle Angle Sum</t>
         </is>
       </c>
-      <c r="D83" s="9" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>8.2.3.1, 8.2.3.2</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t>8.G.5, See eBook</t>
         </is>
@@ -3049,12 +3157,12 @@
           <t>Exterior Angles of Triangles</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>8.2.3.1, 8.3.5.2, 8.3.6.4</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E84" s="9" t="inlineStr">
         <is>
           <t>8.G.5, See eBook</t>
         </is>
@@ -3084,12 +3192,12 @@
           <t>AA Triangle Similarity</t>
         </is>
       </c>
-      <c r="D85" s="9" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>8.3.5.1, 8.3.5.2, 8.3.6.4</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E85" s="9" t="inlineStr">
         <is>
           <t>8.G.5, See eBook</t>
         </is>
@@ -3119,15 +3227,19 @@
           <t>Right, Acute and Obtuse Triangles</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr"/>
-      <c r="E86" s="8" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
         <is>
           <t>8.G.7, See eBook</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.G.7 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.G.7 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
@@ -3150,15 +3262,19 @@
           <t>Right Triangles &amp; Pythagorean Theorem</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr"/>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
         <is>
           <t>8.G.6, 8.G.7, See eBook</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.G.6 (CCSS-M), 8.G.7 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.G.6 (CCSS-M), 8.G.7 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
@@ -3181,15 +3297,19 @@
           <t>Square Root and Irrational Numbers</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr"/>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.6.2, 8.3.6.7, 8.3.6.8, 8.3.7.3</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
         <is>
           <t>8.EE.2, 8.NS.2, See eBook</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.EE.2 (CCSS-M), 8.NS.2 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.6.2 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.7.3 (MN-2022), 8.EE.2 (CCSS-M), 8.NS.2 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
@@ -3212,15 +3332,19 @@
           <t>Rational vs. Irrational Numbers</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr"/>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>8.3.5.1, 8.3.5.2, 8.3.5.3, 8.3.6.2, 8.3.6.7, 8.3.6.8, 8.3.7.3</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
         <is>
           <t>8.EE.2, 8.NS.1, See eBook</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.EE.2 (CCSS-M), 8.NS.1 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.1.1.1 (MN-2007), 8.1.1.2 (MN-2007), 8.3.5.1 (MN-2022), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.6.2 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.7.3 (MN-2022), 8.EE.2 (CCSS-M), 8.NS.1 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
@@ -3243,15 +3367,19 @@
           <t>Pythagorean Theorem in Context</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr"/>
-      <c r="E90" s="8" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
         <is>
           <t>8.G.7, 8.G.8, See eBook</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.G.7 (CCSS-M), 8.G.8 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.G.7 (CCSS-M), 8.G.8 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
@@ -3274,15 +3402,19 @@
           <t>Pythagorean Theorem in 3-D</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr"/>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
         <is>
           <t>8.G.7, See eBook</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.G.7 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.1.1 (MN-2007), 8.3.1.2 (MN-2007), 8.G.7 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
@@ -3306,7 +3438,7 @@
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr"/>
-      <c r="E92" s="8" t="inlineStr">
+      <c r="E92" s="9" t="inlineStr">
         <is>
           <t>8.G.6, See eBook</t>
         </is>
@@ -3349,12 +3481,12 @@
           <t>Volume and Cube Roots</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>8.3.6.7</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
+      <c r="E94" s="9" t="inlineStr">
         <is>
           <t>8.EE.2, See eBook</t>
         </is>
@@ -3384,12 +3516,12 @@
           <t>Surface Area &amp; Volume of Cylinders and Rectangular Prisms</t>
         </is>
       </c>
-      <c r="D95" s="9" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>8.3.6.7</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
+      <c r="E95" s="9" t="inlineStr">
         <is>
           <t>8.G.9, See eBook</t>
         </is>
@@ -3421,12 +3553,12 @@
 Volume of a Prism vs. Pyramid</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>8.3.6.8</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
+      <c r="E96" s="9" t="inlineStr">
         <is>
           <t>8.G.9, See eBook</t>
         </is>
@@ -3456,15 +3588,19 @@
           <t>Volume of Sphere</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr"/>
-      <c r="E97" s="8" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
         <is>
           <t>8.G.9, See eBook</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>8.3.3.1 (MN-2007), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.3.1 (MN-2007), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
@@ -3487,15 +3623,19 @@
           <t>Volume in Context</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr"/>
-      <c r="E98" s="8" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>8.2.3.1, 8.2.3.2, 8.2.3.3, 8.2.4.1, 8.2.4.2, 8.2.4.3</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
         <is>
           <t>8.G.9, See eBook</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>8.3.3.1 (MN-2007), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
+          <t>8.2.3.1 (MN-2022), 8.2.3.2 (MN-2022), 8.2.3.3 (MN-2022), 8.2.4.1 (MN-2022), 8.2.4.2 (MN-2022), 8.2.4.3 (MN-2022), 8.3.3.1 (MN-2007), 8.G.9 (CCSS-M), See eBook (CCSS-M)</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -3518,12 +3658,12 @@
           <t>Indirect Measurement</t>
         </is>
       </c>
-      <c r="D99" s="9" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>8.3.6.9</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
+      <c r="E99" s="9" t="inlineStr">
         <is>
           <t>See eBook</t>
         </is>
@@ -3554,7 +3694,7 @@
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr"/>
-      <c r="E100" s="8" t="inlineStr">
+      <c r="E100" s="9" t="inlineStr">
         <is>
           <t>See eBook</t>
         </is>
@@ -3585,7 +3725,7 @@
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr"/>
-      <c r="E101" s="8" t="inlineStr">
+      <c r="E101" s="9" t="inlineStr">
         <is>
           <t>See eBook</t>
         </is>
@@ -3611,7 +3751,7 @@
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr"/>
-      <c r="D102" s="9" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>8.3.6.9</t>
         </is>
